--- a/Dataset/TO.xlsx
+++ b/Dataset/TO.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="22360" firstSheet="1" activeTab="2"/>
+    <workbookView windowWidth="27900" windowHeight="13360" firstSheet="1" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="All Defects" sheetId="6" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="700" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="132">
   <si>
     <t>Number of Defective Contracts</t>
   </si>
@@ -309,22 +309,7 @@
     <t>0x31ab7dd58bef86b9163e33a7c777f9acce8d8377</t>
   </si>
   <si>
-    <t>reason</t>
-  </si>
-  <si>
-    <t>flag</t>
-  </si>
-  <si>
-    <t>need stage to attack(breakthroughh access control)</t>
-  </si>
-  <si>
-    <t>Multiple access control</t>
-  </si>
-  <si>
-    <t>No critical operation</t>
-  </si>
-  <si>
-    <t>No profit</t>
+    <t>final_flag</t>
   </si>
   <si>
     <t>Vulnerable Contract</t>
@@ -736,11 +721,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="5">
-    <numFmt numFmtId="176" formatCode="0.00_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="0.00_ "/>
   </numFmts>
   <fonts count="28">
     <font>
@@ -819,6 +804,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -827,6 +819,67 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="等线"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -850,74 +903,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="13"/>
       <color theme="3"/>
@@ -927,7 +912,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF9C0006"/>
       <name val="等线"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -972,25 +957,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1014,7 +987,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1026,37 +1065,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1068,25 +1095,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1098,37 +1119,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1140,19 +1131,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1214,6 +1199,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1225,17 +1219,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1257,8 +1240,10 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
@@ -1266,152 +1251,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="15" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="10" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1520,37 +1505,22 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1631,13 +1601,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>6754495</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>1047115</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
+      <xdr:col>22</xdr:col>
       <xdr:colOff>358140</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>2390140</xdr:rowOff>
@@ -1657,7 +1627,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14048740" y="345440"/>
+          <a:off x="7906385" y="345440"/>
           <a:ext cx="11412220" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1673,13 +1643,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
+      <xdr:col>4</xdr:col>
       <xdr:colOff>6641465</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>638810</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
+      <xdr:col>18</xdr:col>
       <xdr:colOff>250825</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>2745105</xdr:rowOff>
@@ -1699,7 +1669,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14048740" y="3256280"/>
+          <a:off x="7906385" y="3256280"/>
           <a:ext cx="8703945" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1988,19 +1958,19 @@
   </cols>
   <sheetData>
     <row r="1" ht="57" customHeight="1" spans="2:6">
-      <c r="B1" s="50" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="50" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="50" t="s">
+      <c r="B1" s="45" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="45" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="50" t="s">
+      <c r="E1" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="50" t="s">
+      <c r="F1" s="45" t="s">
         <v>4</v>
       </c>
     </row>
@@ -2008,19 +1978,19 @@
       <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="50">
+      <c r="B2" s="45">
         <v>45</v>
       </c>
-      <c r="C2" s="50">
+      <c r="C2" s="45">
         <v>77934</v>
       </c>
-      <c r="D2" s="50">
-        <v>0</v>
-      </c>
-      <c r="E2" s="50">
+      <c r="D2" s="45">
+        <v>0</v>
+      </c>
+      <c r="E2" s="45">
         <v>24</v>
       </c>
-      <c r="F2" s="50">
+      <c r="F2" s="45">
         <v>21</v>
       </c>
       <c r="H2" t="s">
@@ -2075,7 +2045,7 @@
       <c r="B1" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="C1" s="48" t="s">
+      <c r="C1" s="43" t="s">
         <v>11</v>
       </c>
       <c r="D1" s="14" t="s">
@@ -2122,7 +2092,7 @@
       <c r="B2" s="14">
         <v>1</v>
       </c>
-      <c r="C2" s="48">
+      <c r="C2" s="43">
         <v>0</v>
       </c>
       <c r="D2" s="14" t="s">
@@ -2169,7 +2139,7 @@
       <c r="B3" s="14">
         <v>1</v>
       </c>
-      <c r="C3" s="48">
+      <c r="C3" s="43">
         <v>0</v>
       </c>
       <c r="D3" s="14" t="s">
@@ -2216,7 +2186,7 @@
       <c r="B4" s="14">
         <v>1</v>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="43">
         <v>0</v>
       </c>
       <c r="D4" s="14" t="s">
@@ -2263,7 +2233,7 @@
       <c r="B5" s="14">
         <v>37</v>
       </c>
-      <c r="C5" s="48">
+      <c r="C5" s="43">
         <v>1.0909e+18</v>
       </c>
       <c r="D5" s="14" t="s">
@@ -2310,7 +2280,7 @@
       <c r="B6" s="14">
         <v>61813</v>
       </c>
-      <c r="C6" s="48">
+      <c r="C6" s="43">
         <v>0</v>
       </c>
       <c r="D6" s="14" t="s">
@@ -2357,7 +2327,7 @@
       <c r="B7" s="14">
         <v>6863</v>
       </c>
-      <c r="C7" s="48">
+      <c r="C7" s="43">
         <v>0</v>
       </c>
       <c r="D7" s="14" t="s">
@@ -2404,7 +2374,7 @@
       <c r="B8" s="14">
         <v>1</v>
       </c>
-      <c r="C8" s="48">
+      <c r="C8" s="43">
         <v>0</v>
       </c>
       <c r="D8" s="14" t="s">
@@ -2451,7 +2421,7 @@
       <c r="B9" s="14">
         <v>1</v>
       </c>
-      <c r="C9" s="48">
+      <c r="C9" s="43">
         <v>0</v>
       </c>
       <c r="D9" s="14" t="s">
@@ -2498,7 +2468,7 @@
       <c r="B10" s="14">
         <v>1</v>
       </c>
-      <c r="C10" s="48">
+      <c r="C10" s="43">
         <v>0</v>
       </c>
       <c r="D10" s="14" t="s">
@@ -2545,7 +2515,7 @@
       <c r="B11" s="14">
         <v>3120</v>
       </c>
-      <c r="C11" s="48">
+      <c r="C11" s="43">
         <v>0</v>
       </c>
       <c r="D11" s="14" t="s">
@@ -2592,7 +2562,7 @@
       <c r="B12" s="14">
         <v>1546</v>
       </c>
-      <c r="C12" s="48">
+      <c r="C12" s="43">
         <v>0</v>
       </c>
       <c r="D12" s="14" t="s">
@@ -2639,7 +2609,7 @@
       <c r="B13" s="14">
         <v>629</v>
       </c>
-      <c r="C13" s="48">
+      <c r="C13" s="43">
         <v>0</v>
       </c>
       <c r="D13" s="14" t="s">
@@ -2686,7 +2656,7 @@
       <c r="B14" s="14">
         <v>2</v>
       </c>
-      <c r="C14" s="48">
+      <c r="C14" s="43">
         <v>0</v>
       </c>
       <c r="D14" s="14" t="s">
@@ -2733,7 +2703,7 @@
       <c r="B15" s="14">
         <v>1</v>
       </c>
-      <c r="C15" s="48">
+      <c r="C15" s="43">
         <v>0</v>
       </c>
       <c r="D15" s="14" t="s">
@@ -2780,7 +2750,7 @@
       <c r="B16" s="14">
         <v>375</v>
       </c>
-      <c r="C16" s="48">
+      <c r="C16" s="43">
         <v>0</v>
       </c>
       <c r="D16" s="14" t="s">
@@ -2827,7 +2797,7 @@
       <c r="B17" s="14">
         <v>1</v>
       </c>
-      <c r="C17" s="48">
+      <c r="C17" s="43">
         <v>0</v>
       </c>
       <c r="D17" s="14" t="s">
@@ -2857,7 +2827,7 @@
       <c r="L17" s="14">
         <v>37</v>
       </c>
-      <c r="M17" s="49">
+      <c r="M17" s="44">
         <v>1.09e+18</v>
       </c>
       <c r="N17" s="14" t="s">
@@ -2874,7 +2844,7 @@
       <c r="B18" s="14">
         <v>1</v>
       </c>
-      <c r="C18" s="48">
+      <c r="C18" s="43">
         <v>0</v>
       </c>
       <c r="D18" s="14" t="s">
@@ -2921,7 +2891,7 @@
       <c r="B19" s="14">
         <v>202</v>
       </c>
-      <c r="C19" s="48">
+      <c r="C19" s="43">
         <v>0</v>
       </c>
       <c r="D19" s="14" t="s">
@@ -2968,7 +2938,7 @@
       <c r="B20" s="14">
         <v>159</v>
       </c>
-      <c r="C20" s="48">
+      <c r="C20" s="43">
         <v>0</v>
       </c>
       <c r="D20" s="14" t="s">
@@ -3015,7 +2985,7 @@
       <c r="B21" s="14">
         <v>155</v>
       </c>
-      <c r="C21" s="48">
+      <c r="C21" s="43">
         <v>0</v>
       </c>
       <c r="D21" s="14" t="s">
@@ -3062,7 +3032,7 @@
       <c r="B22" s="14">
         <v>142</v>
       </c>
-      <c r="C22" s="48">
+      <c r="C22" s="43">
         <v>0</v>
       </c>
       <c r="D22" s="14" t="s">
@@ -3109,7 +3079,7 @@
       <c r="B23" s="14">
         <v>118</v>
       </c>
-      <c r="C23" s="48">
+      <c r="C23" s="43">
         <v>0</v>
       </c>
       <c r="D23" s="14" t="s">
@@ -3156,7 +3126,7 @@
       <c r="B24" s="14">
         <v>1</v>
       </c>
-      <c r="C24" s="48">
+      <c r="C24" s="43">
         <v>0</v>
       </c>
       <c r="D24" s="14" t="s">
@@ -3203,7 +3173,7 @@
       <c r="B25" s="14">
         <v>1</v>
       </c>
-      <c r="C25" s="48">
+      <c r="C25" s="43">
         <v>0</v>
       </c>
       <c r="D25" s="14" t="s">
@@ -3250,7 +3220,7 @@
       <c r="B26" s="14">
         <v>50</v>
       </c>
-      <c r="C26" s="48">
+      <c r="C26" s="43">
         <v>0</v>
       </c>
       <c r="D26" s="14" t="s">
@@ -3297,7 +3267,7 @@
       <c r="B27" s="14">
         <v>22</v>
       </c>
-      <c r="C27" s="48">
+      <c r="C27" s="43">
         <v>0</v>
       </c>
       <c r="D27" s="14" t="s">
@@ -3344,7 +3314,7 @@
       <c r="B28" s="14">
         <v>48</v>
       </c>
-      <c r="C28" s="48">
+      <c r="C28" s="43">
         <v>0</v>
       </c>
       <c r="D28" s="14" t="s">
@@ -3391,7 +3361,7 @@
       <c r="B29" s="14">
         <v>20</v>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="43">
         <v>0</v>
       </c>
       <c r="D29" s="14" t="s">
@@ -3438,7 +3408,7 @@
       <c r="B30" s="14">
         <v>88</v>
       </c>
-      <c r="C30" s="48">
+      <c r="C30" s="43">
         <v>1</v>
       </c>
       <c r="D30" s="14" t="s">
@@ -3485,7 +3455,7 @@
       <c r="B31" s="14">
         <v>19</v>
       </c>
-      <c r="C31" s="48">
+      <c r="C31" s="43">
         <v>0</v>
       </c>
       <c r="D31" s="14" t="s">
@@ -3532,7 +3502,7 @@
       <c r="B32" s="14">
         <v>15</v>
       </c>
-      <c r="C32" s="48">
+      <c r="C32" s="43">
         <v>0</v>
       </c>
       <c r="D32" s="14" t="s">
@@ -3579,7 +3549,7 @@
       <c r="B33" s="14">
         <v>12</v>
       </c>
-      <c r="C33" s="48">
+      <c r="C33" s="43">
         <v>0</v>
       </c>
       <c r="D33" s="14" t="s">
@@ -3626,7 +3596,7 @@
       <c r="B34" s="14">
         <v>13</v>
       </c>
-      <c r="C34" s="48">
+      <c r="C34" s="43">
         <v>0</v>
       </c>
       <c r="D34" s="14" t="s">
@@ -3673,7 +3643,7 @@
       <c r="B35" s="14">
         <v>11</v>
       </c>
-      <c r="C35" s="48">
+      <c r="C35" s="43">
         <v>0</v>
       </c>
       <c r="D35" s="14" t="s">
@@ -3720,7 +3690,7 @@
       <c r="B36" s="14">
         <v>5</v>
       </c>
-      <c r="C36" s="48">
+      <c r="C36" s="43">
         <v>0</v>
       </c>
       <c r="D36" s="14" t="s">
@@ -3767,7 +3737,7 @@
       <c r="B37" s="14">
         <v>6</v>
       </c>
-      <c r="C37" s="48">
+      <c r="C37" s="43">
         <v>0</v>
       </c>
       <c r="D37" s="14" t="s">
@@ -3814,7 +3784,7 @@
       <c r="B38" s="14">
         <v>10</v>
       </c>
-      <c r="C38" s="48">
+      <c r="C38" s="43">
         <v>0</v>
       </c>
       <c r="D38" s="14" t="s">
@@ -3861,7 +3831,7 @@
       <c r="B39" s="14">
         <v>9</v>
       </c>
-      <c r="C39" s="48">
+      <c r="C39" s="43">
         <v>0</v>
       </c>
       <c r="D39" s="14" t="s">
@@ -3908,7 +3878,7 @@
       <c r="B40" s="14">
         <v>2</v>
       </c>
-      <c r="C40" s="48">
+      <c r="C40" s="43">
         <v>0</v>
       </c>
       <c r="D40" s="14" t="s">
@@ -3955,7 +3925,7 @@
       <c r="B41" s="14">
         <v>8</v>
       </c>
-      <c r="C41" s="48">
+      <c r="C41" s="43">
         <v>0</v>
       </c>
       <c r="D41" s="14" t="s">
@@ -4002,7 +3972,7 @@
       <c r="B42" s="14">
         <v>2</v>
       </c>
-      <c r="C42" s="48">
+      <c r="C42" s="43">
         <v>0</v>
       </c>
       <c r="D42" s="14" t="s">
@@ -4049,7 +4019,7 @@
       <c r="B43" s="14">
         <v>8</v>
       </c>
-      <c r="C43" s="48">
+      <c r="C43" s="43">
         <v>0</v>
       </c>
       <c r="D43" s="14" t="s">
@@ -4096,7 +4066,7 @@
       <c r="B44" s="14">
         <v>7</v>
       </c>
-      <c r="C44" s="48">
+      <c r="C44" s="43">
         <v>0</v>
       </c>
       <c r="D44" s="14" t="s">
@@ -4143,7 +4113,7 @@
       <c r="B45" s="14">
         <v>2391</v>
       </c>
-      <c r="C45" s="48">
+      <c r="C45" s="43">
         <v>10</v>
       </c>
       <c r="D45" s="14" t="s">
@@ -4190,7 +4160,7 @@
       <c r="B46" s="14">
         <v>6</v>
       </c>
-      <c r="C46" s="48">
+      <c r="C46" s="43">
         <v>0</v>
       </c>
       <c r="D46" s="14" t="s">
@@ -4242,833 +4212,663 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.4" outlineLevelCol="5"/>
+  <dimension ref="A1:D47"/>
+  <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="12.4" outlineLevelCol="3"/>
   <cols>
-    <col min="1" max="1" width="46.9910714285714" style="9" customWidth="1"/>
-    <col min="2" max="2" width="39.375" style="12" customWidth="1"/>
-    <col min="3" max="3" width="17.4196428571429" style="4" customWidth="1"/>
-    <col min="4" max="4" width="47.1875" customWidth="1"/>
-    <col min="5" max="5" width="8.13392857142857" style="5" customWidth="1"/>
-    <col min="6" max="6" width="29.2857142857143" style="5" customWidth="1"/>
+    <col min="1" max="1" width="17.4196428571429" style="4" customWidth="1"/>
+    <col min="2" max="2" width="47.1875" customWidth="1"/>
+    <col min="3" max="3" width="8.13392857142857" style="5" customWidth="1"/>
+    <col min="4" max="4" width="29.2857142857143" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="13.2" spans="1:6">
-      <c r="A1" s="37"/>
+    <row r="1" ht="13.2" spans="1:4">
+      <c r="A1" s="37" t="s">
+        <v>96</v>
+      </c>
       <c r="B1" s="38" t="s">
-        <v>96</v>
-      </c>
-      <c r="C1" s="39" t="s">
-        <v>97</v>
-      </c>
-      <c r="D1" s="40" t="s">
         <v>9</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="C1" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="D1" s="38" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="2" ht="14" spans="1:6">
-      <c r="A2" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B2" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C2" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D2" s="42" t="s">
+    <row r="2" ht="14" spans="1:4">
+      <c r="A2" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="E2" s="40">
+      <c r="C2" s="38">
         <v>61813</v>
       </c>
-      <c r="F2" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" ht="14" spans="1:6">
-      <c r="A3" s="37"/>
-      <c r="B3" s="43"/>
-      <c r="C3" s="39" t="s">
+      <c r="D2" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" ht="14" spans="1:4">
+      <c r="A3" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="B3" s="39" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="40">
+      <c r="C3" s="38">
         <v>6863</v>
       </c>
-      <c r="F3" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" ht="13.2" spans="1:6">
-      <c r="A4" s="41" t="s">
-        <v>98</v>
+      <c r="D3" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" ht="13.2" spans="1:4">
+      <c r="A4" s="38" t="s">
+        <v>15</v>
       </c>
       <c r="B4" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="40" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="40">
+      <c r="C4" s="38">
         <v>3120</v>
       </c>
-      <c r="F4" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" ht="14" spans="1:6">
-      <c r="A5" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B5" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C5" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="42" t="s">
+      <c r="D4" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" ht="14" spans="1:4">
+      <c r="A5" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="E5" s="40">
+      <c r="C5" s="38">
         <v>2391</v>
       </c>
-      <c r="F5" s="40">
+      <c r="D5" s="38">
         <v>10</v>
       </c>
     </row>
-    <row r="6" ht="14" spans="1:6">
-      <c r="A6" s="37"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="39" t="s">
+    <row r="6" ht="14" spans="1:4">
+      <c r="A6" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="B6" s="39" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="40">
+      <c r="C6" s="38">
         <v>1546</v>
       </c>
-      <c r="F6" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" ht="13.2" spans="1:6">
-      <c r="A7" s="37"/>
+      <c r="D6" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" ht="13.2" spans="1:4">
+      <c r="A7" s="37" t="s">
+        <v>15</v>
+      </c>
       <c r="B7" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C7" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D7" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="40">
+      <c r="C7" s="38">
         <v>629</v>
       </c>
-      <c r="F7" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" ht="14" spans="1:6">
-      <c r="A8" s="37"/>
-      <c r="B8" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="42" t="s">
+      <c r="D7" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" ht="14" spans="1:4">
+      <c r="A8" s="40" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="40">
+      <c r="C8" s="38">
         <v>375</v>
       </c>
-      <c r="F8" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" s="16" customFormat="1" ht="13.2" spans="1:6">
-      <c r="A9" s="45"/>
-      <c r="B9" s="46"/>
-      <c r="C9" s="47" t="s">
+      <c r="D8" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" s="16" customFormat="1" ht="13.2" spans="1:4">
+      <c r="A9" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D9" s="40" t="s">
+      <c r="B9" s="38" t="s">
         <v>36</v>
       </c>
-      <c r="E9" s="40">
+      <c r="C9" s="38">
         <v>202</v>
       </c>
-      <c r="F9" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" ht="14" spans="1:6">
-      <c r="A10" s="37"/>
-      <c r="B10" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D10" s="42" t="s">
+      <c r="D9" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" ht="14" spans="1:4">
+      <c r="A10" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="39" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="40">
+      <c r="C10" s="38">
         <v>159</v>
       </c>
-      <c r="F10" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" ht="13.2" spans="1:6">
-      <c r="A11" s="37"/>
-      <c r="B11" s="43"/>
-      <c r="C11" s="39" t="s">
+      <c r="D10" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" ht="13.2" spans="1:4">
+      <c r="A11" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D11" s="40" t="s">
+      <c r="B11" s="38" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="40">
+      <c r="C11" s="38">
         <v>155</v>
       </c>
-      <c r="F11" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" s="16" customFormat="1" ht="13.2" spans="1:6">
-      <c r="A12" s="45"/>
-      <c r="B12" s="46"/>
-      <c r="C12" s="47" t="s">
+      <c r="D11" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" s="16" customFormat="1" ht="13.2" spans="1:4">
+      <c r="A12" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="40" t="s">
+      <c r="B12" s="38" t="s">
         <v>43</v>
       </c>
-      <c r="E12" s="40">
+      <c r="C12" s="38">
         <v>142</v>
       </c>
-      <c r="F12" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" ht="13.2" spans="1:6">
-      <c r="A13" s="37"/>
-      <c r="B13" s="43"/>
-      <c r="C13" s="39" t="s">
+      <c r="D12" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" ht="13.2" spans="1:4">
+      <c r="A13" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D13" s="40" t="s">
+      <c r="B13" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E13" s="40">
+      <c r="C13" s="38">
         <v>118</v>
       </c>
-      <c r="F13" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" ht="14" spans="1:6">
-      <c r="A14" s="37"/>
-      <c r="B14" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D14" s="42" t="s">
+      <c r="D13" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" ht="14" spans="1:4">
+      <c r="A14" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="E14" s="40">
+      <c r="C14" s="38">
         <v>88</v>
       </c>
-      <c r="F14" s="40">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" ht="13.2" spans="1:6">
-      <c r="A15" s="37"/>
-      <c r="B15" s="43"/>
-      <c r="C15" s="39" t="s">
+      <c r="D14" s="38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" ht="13.2" spans="1:4">
+      <c r="A15" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D15" s="40" t="s">
+      <c r="B15" s="38" t="s">
         <v>51</v>
       </c>
-      <c r="E15" s="40">
+      <c r="C15" s="38">
         <v>50</v>
       </c>
-      <c r="F15" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" ht="13.2" spans="1:6">
-      <c r="A16" s="37"/>
+      <c r="D15" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" ht="13.2" spans="1:4">
+      <c r="A16" s="37" t="s">
+        <v>15</v>
+      </c>
       <c r="B16" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E16" s="40">
+      <c r="C16" s="38">
         <v>48</v>
       </c>
-      <c r="F16" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" ht="13.2" spans="1:6">
-      <c r="A17" s="37"/>
-      <c r="B17" s="43"/>
-      <c r="C17" s="39" t="s">
+      <c r="D16" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="13.2" spans="1:4">
+      <c r="A17" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D17" s="40" t="s">
+      <c r="B17" s="38" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="40">
+      <c r="C17" s="38">
         <v>37</v>
       </c>
-      <c r="F17" s="40">
+      <c r="D17" s="38">
         <v>1.0909e+18</v>
       </c>
     </row>
-    <row r="18" ht="13.2" spans="1:6">
-      <c r="A18" s="41" t="s">
-        <v>98</v>
+    <row r="18" ht="13.2" spans="1:4">
+      <c r="A18" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D18" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="40">
+      <c r="C18" s="38">
         <v>22</v>
       </c>
-      <c r="F18" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" ht="13.2" spans="1:6">
-      <c r="A19" s="37"/>
-      <c r="B19" s="43"/>
-      <c r="C19" s="39" t="s">
+      <c r="D18" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" ht="13.2" spans="1:4">
+      <c r="A19" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D19" s="40" t="s">
+      <c r="B19" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="E19" s="40">
+      <c r="C19" s="38">
         <v>20</v>
       </c>
-      <c r="F19" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" ht="13.2" spans="1:6">
-      <c r="A20" s="37"/>
-      <c r="B20" s="43"/>
-      <c r="C20" s="39" t="s">
+      <c r="D19" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" ht="13.2" spans="1:4">
+      <c r="A20" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="40" t="s">
+      <c r="B20" s="38" t="s">
         <v>60</v>
       </c>
-      <c r="E20" s="40">
+      <c r="C20" s="38">
         <v>19</v>
       </c>
-      <c r="F20" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" ht="13.2" spans="1:6">
-      <c r="A21" s="37"/>
-      <c r="B21" s="43"/>
-      <c r="C21" s="39" t="s">
+      <c r="D20" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="13.2" spans="1:4">
+      <c r="A21" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D21" s="40" t="s">
+      <c r="B21" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="40">
-        <v>15</v>
-      </c>
-      <c r="F21" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" ht="13.2" spans="1:6">
-      <c r="A22" s="37"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="39" t="s">
+      <c r="C21" s="38">
+        <v>15</v>
+      </c>
+      <c r="D21" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" ht="13.2" spans="1:4">
+      <c r="A22" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="B22" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="E22" s="40">
+      <c r="C22" s="38">
         <v>13</v>
       </c>
-      <c r="F22" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" ht="13.2" spans="1:6">
-      <c r="A23" s="41" t="s">
-        <v>98</v>
+      <c r="D22" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="13.2" spans="1:4">
+      <c r="A23" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="B23" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D23" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="E23" s="40">
+      <c r="C23" s="38">
         <v>12</v>
       </c>
-      <c r="F23" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" ht="13.2" spans="1:6">
-      <c r="A24" s="37"/>
+      <c r="D23" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" ht="13.2" spans="1:4">
+      <c r="A24" s="37" t="s">
+        <v>21</v>
+      </c>
       <c r="B24" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C24" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="38">
+        <v>11</v>
+      </c>
+      <c r="D24" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" ht="13.2" spans="1:4">
+      <c r="A25" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B25" s="38" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="38">
+        <v>10</v>
+      </c>
+      <c r="D25" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" ht="13.2" spans="1:4">
+      <c r="A26" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="38">
+        <v>9</v>
+      </c>
+      <c r="D26" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" ht="13.2" spans="1:4">
+      <c r="A27" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B27" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="38">
+        <v>8</v>
+      </c>
+      <c r="D27" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" ht="13.2" spans="1:4">
+      <c r="A28" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="E24" s="40">
-        <v>11</v>
-      </c>
-      <c r="F24" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" ht="13.2" spans="1:6">
-      <c r="A25" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B25" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D25" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="E25" s="40">
-        <v>10</v>
-      </c>
-      <c r="F25" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" ht="13.2" spans="1:6">
-      <c r="A26" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B26" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="E26" s="40">
-        <v>9</v>
-      </c>
-      <c r="F26" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" ht="13.2" spans="1:6">
-      <c r="A27" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B27" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D27" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="E27" s="40">
+      <c r="B28" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C28" s="38">
         <v>8</v>
       </c>
-      <c r="F27" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" ht="13.2" spans="1:6">
-      <c r="A28" s="37"/>
-      <c r="B28" s="43"/>
-      <c r="C28" s="41" t="s">
+      <c r="D28" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" ht="13.2" spans="1:4">
+      <c r="A29" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="E28" s="40">
-        <v>8</v>
-      </c>
-      <c r="F28" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" ht="13.2" spans="1:6">
-      <c r="A29" s="37"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="41" t="s">
+      <c r="B29" s="38" t="s">
+        <v>78</v>
+      </c>
+      <c r="C29" s="38">
+        <v>7</v>
+      </c>
+      <c r="D29" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" ht="13.2" spans="1:4">
+      <c r="A30" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" s="38">
+        <v>6</v>
+      </c>
+      <c r="D30" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" ht="13.2" spans="1:4">
+      <c r="A31" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D29" s="40" t="s">
-        <v>78</v>
-      </c>
-      <c r="E29" s="40">
-        <v>7</v>
-      </c>
-      <c r="F29" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" ht="13.2" spans="1:6">
-      <c r="A30" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B30" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C30" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="D30" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="40">
+      <c r="B31" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C31" s="38">
         <v>6</v>
       </c>
-      <c r="F30" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" ht="13.2" spans="1:6">
-      <c r="A31" s="37"/>
-      <c r="B31" s="43"/>
-      <c r="C31" s="39" t="s">
+      <c r="D31" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" ht="13.2" spans="1:4">
+      <c r="A32" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D31" s="40" t="s">
-        <v>80</v>
-      </c>
-      <c r="E31" s="40">
-        <v>6</v>
-      </c>
-      <c r="F31" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" ht="13.2" spans="1:6">
-      <c r="A32" s="37"/>
-      <c r="B32" s="43"/>
-      <c r="C32" s="39" t="s">
+      <c r="B32" s="38" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="38">
+        <v>5</v>
+      </c>
+      <c r="D32" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" ht="13.2" spans="1:4">
+      <c r="A33" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D32" s="40" t="s">
-        <v>84</v>
-      </c>
-      <c r="E32" s="40">
-        <v>5</v>
-      </c>
-      <c r="F32" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" ht="13.2" spans="1:6">
-      <c r="A33" s="37"/>
-      <c r="B33" s="43"/>
-      <c r="C33" s="39" t="s">
+      <c r="B33" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C33" s="38">
+        <v>2</v>
+      </c>
+      <c r="D33" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" ht="13.2" spans="1:4">
+      <c r="A34" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="38">
+        <v>2</v>
+      </c>
+      <c r="D34" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" ht="13.2" spans="1:4">
+      <c r="A35" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B35" s="38" t="s">
+        <v>47</v>
+      </c>
+      <c r="C35" s="38">
+        <v>2</v>
+      </c>
+      <c r="D35" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" ht="13.2" spans="1:4">
+      <c r="A36" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>54</v>
+      </c>
+      <c r="C36" s="38">
+        <v>1</v>
+      </c>
+      <c r="D36" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" ht="13.2" spans="1:4">
+      <c r="A37" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D33" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="E33" s="40">
-        <v>2</v>
-      </c>
-      <c r="F33" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" ht="13.2" spans="1:6">
-      <c r="A34" s="37"/>
-      <c r="B34" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D34" s="40" t="s">
-        <v>86</v>
-      </c>
-      <c r="E34" s="40">
-        <v>2</v>
-      </c>
-      <c r="F34" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" ht="13.2" spans="1:6">
-      <c r="A35" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B35" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C35" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="40" t="s">
-        <v>47</v>
-      </c>
-      <c r="E35" s="40">
-        <v>2</v>
-      </c>
-      <c r="F35" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" ht="13.2" spans="1:6">
-      <c r="A36" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B36" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C36" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D36" s="40" t="s">
-        <v>54</v>
-      </c>
-      <c r="E36" s="40">
-        <v>1</v>
-      </c>
-      <c r="F36" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" ht="13.2" spans="1:6">
-      <c r="A37" s="37"/>
-      <c r="B37" s="43"/>
-      <c r="C37" s="39" t="s">
+      <c r="B37" s="38" t="s">
+        <v>18</v>
+      </c>
+      <c r="C37" s="38">
+        <v>1</v>
+      </c>
+      <c r="D37" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="13.2" spans="1:4">
+      <c r="A38" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D37" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="E37" s="40">
-        <v>1</v>
-      </c>
-      <c r="F37" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" ht="13.2" spans="1:6">
-      <c r="A38" s="37"/>
-      <c r="B38" s="43"/>
-      <c r="C38" s="39" t="s">
+      <c r="B38" s="38" t="s">
+        <v>22</v>
+      </c>
+      <c r="C38" s="38">
+        <v>1</v>
+      </c>
+      <c r="D38" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" ht="14" spans="1:4">
+      <c r="A39" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B39" s="39" t="s">
+        <v>32</v>
+      </c>
+      <c r="C39" s="38">
+        <v>1</v>
+      </c>
+      <c r="D39" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" ht="13.2" spans="1:4">
+      <c r="A40" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D38" s="40" t="s">
-        <v>22</v>
-      </c>
-      <c r="E38" s="40">
-        <v>1</v>
-      </c>
-      <c r="F38" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" ht="14" spans="1:6">
-      <c r="A39" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B39" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D39" s="42" t="s">
-        <v>32</v>
-      </c>
-      <c r="E39" s="40">
-        <v>1</v>
-      </c>
-      <c r="F39" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" ht="13.2" spans="1:6">
-      <c r="A40" s="37"/>
-      <c r="B40" s="43"/>
-      <c r="C40" s="39" t="s">
+      <c r="B40" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C40" s="38">
+        <v>1</v>
+      </c>
+      <c r="D40" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" ht="13.2" spans="1:4">
+      <c r="A41" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D40" s="40" t="s">
-        <v>35</v>
-      </c>
-      <c r="E40" s="40">
-        <v>1</v>
-      </c>
-      <c r="F40" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" ht="13.2" spans="1:6">
-      <c r="A41" s="37"/>
-      <c r="B41" s="43"/>
-      <c r="C41" s="39" t="s">
+      <c r="B41" s="38" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" s="38">
+        <v>1</v>
+      </c>
+      <c r="D41" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" ht="13.2" spans="1:4">
+      <c r="A42" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D41" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="E41" s="40">
-        <v>1</v>
-      </c>
-      <c r="F41" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" ht="13.2" spans="1:6">
-      <c r="A42" s="37"/>
       <c r="B42" s="38" t="s">
-        <v>101</v>
-      </c>
-      <c r="C42" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="C42" s="38">
+        <v>1</v>
+      </c>
+      <c r="D42" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" ht="13.2" spans="1:4">
+      <c r="A43" s="37" t="s">
         <v>21</v>
       </c>
-      <c r="D42" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="40">
-        <v>1</v>
-      </c>
-      <c r="F42" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" ht="13.2" spans="1:6">
-      <c r="A43" s="37"/>
-      <c r="B43" s="43"/>
-      <c r="C43" s="39" t="s">
-        <v>21</v>
-      </c>
-      <c r="D43" s="40" t="s">
+      <c r="B43" s="38" t="s">
         <v>55</v>
       </c>
-      <c r="E43" s="40">
-        <v>1</v>
-      </c>
-      <c r="F43" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" ht="13.2" spans="1:6">
-      <c r="A44" s="41" t="s">
-        <v>98</v>
+      <c r="C43" s="38">
+        <v>1</v>
+      </c>
+      <c r="D43" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" ht="13.2" spans="1:4">
+      <c r="A44" s="37" t="s">
+        <v>15</v>
       </c>
       <c r="B44" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C44" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D44" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="E44" s="40">
-        <v>1</v>
-      </c>
-      <c r="F44" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" ht="14" spans="1:6">
-      <c r="A45" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="B45" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="C45" s="39" t="s">
-        <v>15</v>
-      </c>
-      <c r="D45" s="42" t="s">
+      <c r="C44" s="38">
+        <v>1</v>
+      </c>
+      <c r="D44" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" ht="14" spans="1:4">
+      <c r="A45" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="B45" s="39" t="s">
         <v>69</v>
       </c>
-      <c r="E45" s="40">
-        <v>1</v>
-      </c>
-      <c r="F45" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" ht="14" spans="1:6">
-      <c r="A46" s="37"/>
-      <c r="B46" s="38" t="s">
-        <v>100</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>15</v>
-      </c>
-      <c r="D46" s="42" t="s">
+      <c r="C45" s="38">
+        <v>1</v>
+      </c>
+      <c r="D45" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" ht="14" spans="1:4">
+      <c r="A46" s="42" t="s">
+        <v>15</v>
+      </c>
+      <c r="B46" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E46" s="40">
-        <v>1</v>
-      </c>
-      <c r="F46" s="40">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" ht="13.2" spans="4:6">
-      <c r="D47" s="14"/>
-      <c r="E47" s="15"/>
-      <c r="F47" s="15"/>
+      <c r="C46" s="38">
+        <v>1</v>
+      </c>
+      <c r="D46" s="38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" ht="13.2" spans="2:4">
+      <c r="B47" s="14"/>
+      <c r="C47" s="15"/>
+      <c r="D47" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511805555555556" footer="0.511805555555556"/>
@@ -5090,13 +4890,13 @@
   <sheetData>
     <row r="2" ht="14" spans="2:4">
       <c r="B2" s="17" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="C2" s="17" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D2" s="18" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" ht="13.2" spans="2:4">
@@ -5112,31 +4912,31 @@
     </row>
     <row r="4" s="16" customFormat="1" ht="13.2" spans="2:4">
       <c r="B4" s="19" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C4" s="19"/>
       <c r="D4" s="21"/>
     </row>
     <row r="5" s="16" customFormat="1" spans="2:4">
       <c r="B5" s="22" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D5" s="24"/>
     </row>
     <row r="6" s="16" customFormat="1" ht="13.2" spans="2:4">
       <c r="B6" s="25"/>
       <c r="C6" s="24" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D6" s="24"/>
     </row>
     <row r="7" s="16" customFormat="1" ht="14" spans="2:4">
       <c r="B7" s="26"/>
       <c r="C7" s="27" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="D7" s="21"/>
     </row>
@@ -5154,39 +4954,39 @@
     <row r="9" s="16" customFormat="1" ht="14" customHeight="1" spans="2:4">
       <c r="B9" s="26"/>
       <c r="C9" s="28" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D9" s="29"/>
     </row>
     <row r="10" s="16" customFormat="1" ht="13.2" spans="2:4">
       <c r="B10" s="30" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C10" s="24" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D10" s="24"/>
     </row>
     <row r="11" s="16" customFormat="1" ht="13.2" spans="2:4">
       <c r="B11" s="31"/>
       <c r="C11" s="24" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="D11" s="24"/>
     </row>
     <row r="12" s="16" customFormat="1" ht="13.2" spans="2:4">
       <c r="B12" s="31"/>
       <c r="C12" s="24" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D12" s="24"/>
     </row>
     <row r="13" s="16" customFormat="1" spans="2:4">
       <c r="B13" s="32" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C13" s="23" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D13" s="24"/>
     </row>
@@ -5203,27 +5003,27 @@
     </row>
     <row r="15" ht="13.2" spans="2:4">
       <c r="B15" s="33" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="C15" s="33"/>
       <c r="D15" s="34"/>
     </row>
     <row r="20" spans="2:3">
       <c r="B20" s="23" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C20" s="23"/>
     </row>
     <row r="21" s="16" customFormat="1" ht="16" customHeight="1" spans="2:5">
       <c r="B21" s="25" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D21" s="36"/>
       <c r="E21" s="16" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -5273,13 +5073,13 @@
     </row>
     <row r="2" ht="27" spans="1:5">
       <c r="A2" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D2" s="6">
         <v>61813</v>
@@ -5290,7 +5090,7 @@
     </row>
     <row r="3" ht="13.2" spans="1:5">
       <c r="A3" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>15</v>
@@ -5307,13 +5107,13 @@
     </row>
     <row r="4" ht="27" spans="1:5">
       <c r="A4" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D4" s="6">
         <v>2391</v>
@@ -5324,7 +5124,7 @@
     </row>
     <row r="5" ht="13.2" spans="1:5">
       <c r="A5" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>15</v>
@@ -5341,7 +5141,7 @@
     </row>
     <row r="6" ht="14" spans="1:5">
       <c r="A6" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>15</v>
@@ -5358,13 +5158,13 @@
     </row>
     <row r="7" ht="27" spans="1:5">
       <c r="A7" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D7" s="6">
         <v>159</v>
@@ -5375,13 +5175,13 @@
     </row>
     <row r="8" ht="27" spans="1:5">
       <c r="A8" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D8" s="6">
         <v>88</v>
@@ -5392,7 +5192,7 @@
     </row>
     <row r="9" ht="13.2" spans="1:5">
       <c r="A9" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>15</v>
@@ -5409,7 +5209,7 @@
     </row>
     <row r="10" ht="13.2" spans="1:5">
       <c r="A10" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>15</v>
@@ -5426,7 +5226,7 @@
     </row>
     <row r="11" ht="13.2" spans="1:5">
       <c r="A11" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>15</v>
@@ -5443,7 +5243,7 @@
     </row>
     <row r="12" ht="13.2" spans="1:5">
       <c r="A12" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>15</v>
@@ -5460,7 +5260,7 @@
     </row>
     <row r="13" ht="13.2" spans="1:5">
       <c r="A13" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>15</v>
@@ -5477,7 +5277,7 @@
     </row>
     <row r="14" ht="13.2" spans="1:5">
       <c r="A14" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>15</v>
@@ -5494,7 +5294,7 @@
     </row>
     <row r="15" ht="13.2" spans="1:5">
       <c r="A15" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B15" s="9" t="s">
         <v>15</v>
@@ -5511,7 +5311,7 @@
     </row>
     <row r="16" ht="13.2" spans="1:5">
       <c r="A16" s="3" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>15</v>
@@ -5528,7 +5328,7 @@
     </row>
     <row r="17" ht="13.2" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>15</v>
@@ -5545,7 +5345,7 @@
     </row>
     <row r="18" ht="13.2" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>15</v>
@@ -5562,13 +5362,13 @@
     </row>
     <row r="19" ht="27" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D19" s="6">
         <v>1</v>
@@ -5579,7 +5379,7 @@
     </row>
     <row r="20" ht="13.2" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>15</v>
@@ -5596,13 +5396,13 @@
     </row>
     <row r="21" ht="27" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D21" s="6">
         <v>1</v>
@@ -5613,13 +5413,13 @@
     </row>
     <row r="22" ht="40" spans="1:5">
       <c r="A22" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>125</v>
-      </c>
-      <c r="B22" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="C22" s="7" t="s">
-        <v>130</v>
       </c>
       <c r="D22" s="6">
         <v>1</v>
@@ -5630,7 +5430,7 @@
     </row>
     <row r="23" ht="25" spans="2:5">
       <c r="B23" s="9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>74</v>
@@ -5644,7 +5444,7 @@
     </row>
     <row r="24" ht="25" spans="2:5">
       <c r="B24" s="9" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>78</v>
@@ -5661,7 +5461,7 @@
         <v>21</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D25" s="6">
         <v>6863</v>
@@ -5828,7 +5628,7 @@
     </row>
     <row r="37" ht="25" customHeight="1" spans="1:5">
       <c r="A37" s="12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>21</v>
@@ -5943,7 +5743,7 @@
     </row>
     <row r="45" ht="25" spans="1:5">
       <c r="A45" s="12" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>21</v>
@@ -5998,18 +5798,18 @@
   <sheetData>
     <row r="2" ht="50" spans="2:3">
       <c r="B2" s="1" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="C2" s="2"/>
     </row>
     <row r="3" spans="2:2">
       <c r="B3" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
     </row>
     <row r="4" ht="38" spans="2:2">
       <c r="B4" s="1" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
     </row>
   </sheetData>
